--- a/data/Ontologies_forRepo.xlsx
+++ b/data/Ontologies_forRepo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK159"/>
+  <dimension ref="A1:CK160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1909,12 +1909,12 @@
       <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>n0c57a745c4284e78900fbd8590c8cd3fb1</t>
+          <t>na372d9a0e896435aa4a5b30b189f3eafb1</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>n0c57a745c4284e78900fbd8590c8cd3fb1</t>
+          <t>na372d9a0e896435aa4a5b30b189f3eafb1</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr"/>
@@ -2179,12 +2179,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>n4fc5505c59bd47e7a755ca71d9d884a9b1</t>
+          <t>n81637741c1504a199b1297ba0d2dfcdab1</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>n4fc5505c59bd47e7a755ca71d9d884a9b1</t>
+          <t>n81637741c1504a199b1297ba0d2dfcdab1</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr"/>
@@ -3198,10 +3198,10 @@
       </c>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>0.08</v>
+        <v>0.74</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.08</v>
+        <v>0.74</v>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Building Element Ontology</t>
+          <t>Built Element Ontology</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Building Element Ontology</t>
+          <t>Built Element Ontology</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>The Building Element Ontology provides an ontology based on the IfcBuildingElement subtree in the IFC specification, containing a taxonomy of classes that allow to define common building elements.</t>
+          <t>OWL ontology to describe built elements in the built environment. It is based on the Product ontology descibed in IFC (Insutry Foundation Classes) schema.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -5626,30 +5626,18 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2018-12-27</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2018-12-27</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t xml:space="preserve">CC BY 3.0 </t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>https://creativecommons.org/licenses/by/1.0/</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://creativecommons.org/licenses/by/1.0/</t>
+          <t xml:space="preserve">CC BY 3.0 </t>
         </is>
       </c>
       <c r="U19" t="n">
@@ -5657,12 +5645,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>December 27th 2018</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>December 27th 2018</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -5671,12 +5659,12 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>dc, dcterms, gr, vann, voaf, vs, foaf, schema</t>
+          <t>cc, dc, vann, schema</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>dc, dcterms, gr, vann, voaf, vs, foaf, schema</t>
+          <t>cc, dc, vann, schema</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5686,12 +5674,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>https://pi.pauwel.be/voc/buildingelement, https://pi.pauwel.be/voc/buildingelement#</t>
+          <t>https://w3id.org/beo#</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>https://w3id.org/beo#, https://pi.pauwel.be/voc/buildingelement</t>
+          <t>https://w3id.org/beo#</t>
         </is>
       </c>
       <c r="AG19" t="b">
@@ -5720,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>100</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="b">
@@ -5731,12 +5719,12 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>bimxel, contax, dtc, facility, fmo, hbpo, hmo, rdo</t>
+          <t>bimxel</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>bimxel, contax, dtc, facility, fmo, hbpo, hmo, rdo</t>
+          <t>bimxel</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr"/>
@@ -5794,32 +5782,32 @@
       <c r="BP19" t="inlineStr"/>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>n792dd20240f9439ebaa3eef5823ec1aab1</t>
+          <t>Carlos Ramonell Cazador (carlos.ramonell@upc.edu)</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>n792dd20240f9439ebaa3eef5823ec1aab1</t>
+          <t>Carlos Ramonell Cazador (carlos.ramonell@upc.edu)</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr"/>
       <c r="BT19" t="inlineStr"/>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {gr: http://purl.org/goodrelations/v1#}, {vann: http://purl.org/vocab/vann/}, {voaf: http://purl.org/vocommons/voaf#}, {None: http://www.buildingsmart-tech.org/ifcOWL/IFC4_ADD2#}, {vs: http://www.w3.org/2003/06/sw-vocab-status/ns#}, {foaf: http://xmlns.com/foaf/0.1/}, {None: https://creativecommons.org/licenses/by/1.0/}, {schema: https://schema.org/}</t>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {cc: http://creativecommons.org/ns#}, {dc: http://purl.org/dc/elements/1.1/}, {vann: http://purl.org/vocab/vann/}, {schema: https://schema.org/}</t>
         </is>
       </c>
       <c r="BV19" t="n">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="BW19" t="n">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="BX19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="BY19" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="BZ19" t="n">
         <v>0</v>
@@ -5843,7 +5831,7 @@
         <v>2</v>
       </c>
       <c r="CG19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="CH19" t="b">
         <v>1</v>
@@ -7737,12 +7725,12 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>bcfowl, bcore, bcorezones, bimxel, building, contax, cto, dor, dot, dtc, eco, facility, hbpo, icdd2ams, ioc, unocs, xemo</t>
+          <t>bcfowl, bcore, bcorezones, bimxel, building, contax, cto, dor, dot, dtc, eco, facility, fisa, hbpo, icdd2ams, ioc, unocs, xemo</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>bcfowl, bcore, bcorezones, bimxel, building, contax, cto, dor, dot, dtc, eco, facility, hbpo, icdd2ams, ioc, unocs, xemo</t>
+          <t>bcfowl, bcore, bcorezones, bimxel, building, contax, cto, dor, dot, dtc, eco, facility, fisa, hbpo, icdd2ams, ioc, unocs, xemo</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr"/>
@@ -8093,12 +8081,12 @@
       <c r="BP28" t="inlineStr"/>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>n25fdaae2187b4732ad28564a88fffcf8b8, n25fdaae2187b4732ad28564a88fffcf8b9, n25fdaae2187b4732ad28564a88fffcf8b10, n25fdaae2187b4732ad28564a88fffcf8b11</t>
+          <t>nea0380311087496ab11fce5519ea7fa2b8, nea0380311087496ab11fce5519ea7fa2b9, nea0380311087496ab11fce5519ea7fa2b10, nea0380311087496ab11fce5519ea7fa2b11</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>n25fdaae2187b4732ad28564a88fffcf8b8, n25fdaae2187b4732ad28564a88fffcf8b9, n25fdaae2187b4732ad28564a88fffcf8b10, n25fdaae2187b4732ad28564a88fffcf8b11</t>
+          <t>nea0380311087496ab11fce5519ea7fa2b8, nea0380311087496ab11fce5519ea7fa2b9, nea0380311087496ab11fce5519ea7fa2b10, nea0380311087496ab11fce5519ea7fa2b11</t>
         </is>
       </c>
       <c r="BS28" t="inlineStr"/>
@@ -8633,22 +8621,22 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>ne133dfb83edd42efac143157b4fefb61b7274</t>
+          <t>n9d7ba3da0e374d8d95788e3e21f34c4bb7274</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>ne133dfb83edd42efac143157b4fefb61b7274</t>
+          <t>n9d7ba3da0e374d8d95788e3e21f34c4bb7274</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>ne133dfb83edd42efac143157b4fefb61b7276</t>
+          <t>n9d7ba3da0e374d8d95788e3e21f34c4bb7276</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>ne133dfb83edd42efac143157b4fefb61b7276</t>
+          <t>n9d7ba3da0e374d8d95788e3e21f34c4bb7276</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -8922,12 +8910,12 @@
       <c r="BP31" t="inlineStr"/>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>ne7f672fa5bc14f719be055baeb19df8db1, ne7f672fa5bc14f719be055baeb19df8db2</t>
+          <t>n7a67f68bacf24ea89ebcbbdd2100d642b1, n7a67f68bacf24ea89ebcbbdd2100d642b2</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>ne7f672fa5bc14f719be055baeb19df8db1, ne7f672fa5bc14f719be055baeb19df8db2</t>
+          <t>n7a67f68bacf24ea89ebcbbdd2100d642b1, n7a67f68bacf24ea89ebcbbdd2100d642b2</t>
         </is>
       </c>
       <c r="BS31" t="inlineStr"/>
@@ -9079,12 +9067,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>io, kpi, mat, saref, bot</t>
+          <t>io, kpi, mat, wgs84_pos, saref, bot</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>io, kpi, mat, saref, bot</t>
+          <t>io, kpi, mat, wgs84_pos, saref, bot</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -9094,12 +9082,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>dc, dcterms, wgs84_pos</t>
+          <t>dc, dcterms</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>dc, dcterms, wgs84_pos</t>
+          <t>dc, dcterms</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -9235,7 +9223,7 @@
       </c>
       <c r="BU32" t="inlineStr">
         <is>
-          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {None: http://bimerr.iot.linkeddata.es/def/information-objects#}, {kpi: http://bimerr.iot.linkeddata.es/def/key-performance-indicator#}, {mat: http://bimerr.iot.linkeddata.es/def/material-properties#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {wgs84_pos: http://www.w3.org/2003/01/geo/wgs84_pos#}, {saref: https://saref.etsi.org/core/}, {bot: https://w3id.org/bot#}, {None: https://w3id.org/def/saref4bldg#}</t>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {None: http://bimerr.iot.linkeddata.es/def/information-objects#}, {kpi: http://bimerr.iot.linkeddata.es/def/key-performance-indicator#}, {mat: http://bimerr.iot.linkeddata.es/def/material-properties#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {geo: http://www.w3.org/2003/01/geo/wgs84_pos#}, {saref: https://saref.etsi.org/core/}, {bot: https://w3id.org/bot#}, {None: https://w3id.org/def/saref4bldg#}</t>
         </is>
       </c>
       <c r="BV32" t="n">
@@ -9693,12 +9681,12 @@
       <c r="BP34" t="inlineStr"/>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>n335d3de89b504e7eb2517146540c8489b1</t>
+          <t>ned4694ffe3c243a9be0692d47f42477eb1</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>n335d3de89b504e7eb2517146540c8489b1</t>
+          <t>ned4694ffe3c243a9be0692d47f42477eb1</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr"/>
@@ -10410,12 +10398,12 @@
       <c r="BP37" t="inlineStr"/>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>n97a3dbfcc6d54fce80f5e044458ef9f8b3, n97a3dbfcc6d54fce80f5e044458ef9f8b4</t>
+          <t>n603cfb36249a4caab8125ae6cd25b618b3, n603cfb36249a4caab8125ae6cd25b618b4</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>n97a3dbfcc6d54fce80f5e044458ef9f8b3, n97a3dbfcc6d54fce80f5e044458ef9f8b4</t>
+          <t>n603cfb36249a4caab8125ae6cd25b618b3, n603cfb36249a4caab8125ae6cd25b618b4</t>
         </is>
       </c>
       <c r="BS37" t="inlineStr"/>
@@ -10776,12 +10764,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>beo, bot, cto, dot, fog, mep, omg, opm</t>
+          <t>bot, cto, dot, fog, mep, omg, opm</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>beo, bot, cto, dot, fog, mep, omg, opm</t>
+          <t>bot, cto, dot, fog, mep, omg, opm</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -10791,12 +10779,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>cc, dbr, dcat, dct, furn, gvp, mdcs, pi, schema, skos, vann, vcard, voaf</t>
+          <t>beo, cc, dbr, dcat, dct, furn, gvp, mdcs, pi, schema, skos, vann, vcard, voaf</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>cc, dbr, dcat, dct, furn, gvp, mdcs, pi, schema, skos, vann, vcard, voaf</t>
+          <t>beo, cc, dbr, dcat, dct, furn, gvp, mdcs, pi, schema, skos, vann, vcard, voaf</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr"/>
@@ -10902,12 +10890,12 @@
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>ne2fe3dbc8195492490f04b7f26ac90a6b1</t>
+          <t>n6eed0926b43e4e15aedb659615cf0188b1</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
         <is>
-          <t>ne2fe3dbc8195492490f04b7f26ac90a6b1</t>
+          <t>n6eed0926b43e4e15aedb659615cf0188b1</t>
         </is>
       </c>
       <c r="BS39" t="inlineStr"/>
@@ -11209,12 +11197,12 @@
       <c r="BP40" t="inlineStr"/>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>ndc392392f52c42fabdc5f73f8607d186b3, ndc392392f52c42fabdc5f73f8607d186b4</t>
+          <t>ne3b5e7cdd3394ff1b34445fced8654c9b3, ne3b5e7cdd3394ff1b34445fced8654c9b4</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
         <is>
-          <t>ndc392392f52c42fabdc5f73f8607d186b3, ndc392392f52c42fabdc5f73f8607d186b4</t>
+          <t>ne3b5e7cdd3394ff1b34445fced8654c9b3, ne3b5e7cdd3394ff1b34445fced8654c9b4</t>
         </is>
       </c>
       <c r="BS40" t="inlineStr"/>
@@ -11516,12 +11504,12 @@
       <c r="BP41" t="inlineStr"/>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>n1472289031cd4cbbb7ff09f6a812799db3, n1472289031cd4cbbb7ff09f6a812799db4</t>
+          <t>neeb0ec8ef62249c98da3084bab764cfeb3, neeb0ec8ef62249c98da3084bab764cfeb4</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>n1472289031cd4cbbb7ff09f6a812799db3, n1472289031cd4cbbb7ff09f6a812799db4</t>
+          <t>neeb0ec8ef62249c98da3084bab764cfeb3, neeb0ec8ef62249c98da3084bab764cfeb4</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr"/>
@@ -11816,12 +11804,12 @@
       <c r="BP42" t="inlineStr"/>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>n0db3cd2287724bd1833c56d13f3b5a49b1</t>
+          <t>n9d5e7733340c4a93bcfa432aa0f5ce69b1</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
         <is>
-          <t>n0db3cd2287724bd1833c56d13f3b5a49b1</t>
+          <t>n9d5e7733340c4a93bcfa432aa0f5ce69b1</t>
         </is>
       </c>
       <c r="BS42" t="inlineStr"/>
@@ -12108,22 +12096,22 @@
       <c r="BP43" t="inlineStr"/>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>n84bc2dd22a574d8fa2a09fa2b2cfbcc8b1</t>
+          <t>n5819dd18daf14340865d08845eda1fffb1</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>n84bc2dd22a574d8fa2a09fa2b2cfbcc8b1</t>
+          <t>n5819dd18daf14340865d08845eda1fffb1</t>
         </is>
       </c>
       <c r="BS43" t="inlineStr">
         <is>
-          <t>n84bc2dd22a574d8fa2a09fa2b2cfbcc8b3</t>
+          <t>n5819dd18daf14340865d08845eda1fffb3</t>
         </is>
       </c>
       <c r="BT43" t="inlineStr">
         <is>
-          <t>n84bc2dd22a574d8fa2a09fa2b2cfbcc8b3</t>
+          <t>n5819dd18daf14340865d08845eda1fffb3</t>
         </is>
       </c>
       <c r="BU43" t="inlineStr">
@@ -16689,12 +16677,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>cc, dcterms, gr, vann, foaf</t>
+          <t>cc, ssn, dcterms, gr, vann, DUL, foaf</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>cc, dcterms, gr, vann, foaf</t>
+          <t>cc, ssn, dcterms, gr, vann, DUL, foaf</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr"/>
@@ -16804,7 +16792,7 @@
       <c r="BT60" t="inlineStr"/>
       <c r="BU60" t="inlineStr">
         <is>
-          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {cc: http://creativecommons.org/ns#}, {None: http://elite.polito.it/ontologies/}, {None: http://elite.polito.it/ontologies/muo-vocab.owl#}, {None: http://purl.oclc.org/NET/ssnx/ssn#}, {dcterms: http://purl.org/dc/terms/}, {gr: http://purl.org/goodrelations/v1#}, {vann: http://purl.org/vocab/vann/}, {None: http://www.loa-cnr.it/ontologies/DUL.owl#}, {foaf: http://xmlns.com/foaf/0.1/}</t>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {cc: http://creativecommons.org/ns#}, {None: http://elite.polito.it/ontologies/}, {None: http://elite.polito.it/ontologies/muo-vocab.owl#}, {ssn: http://purl.oclc.org/NET/ssnx/ssn#}, {dcterms: http://purl.org/dc/terms/}, {gr: http://purl.org/goodrelations/v1#}, {vann: http://purl.org/vocab/vann/}, {DUL: http://www.loa-cnr.it/ontologies/DUL.owl#}, {foaf: http://xmlns.com/foaf/0.1/}</t>
         </is>
       </c>
       <c r="BV60" t="n">
@@ -17402,12 +17390,12 @@
       </c>
       <c r="BQ62" t="inlineStr">
         <is>
-          <t>nc478bf0f2ced4970a0453c41e2d4a214b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
+          <t>nd8bda84181524edca669680d292a20f4b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
         </is>
       </c>
       <c r="BR62" t="inlineStr">
         <is>
-          <t>nc478bf0f2ced4970a0453c41e2d4a214b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
+          <t>nd8bda84181524edca669680d292a20f4b1, https://www.researchgate.net/profile/Mathias_Bonduel</t>
         </is>
       </c>
       <c r="BS62" t="inlineStr"/>
@@ -17838,12 +17826,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>geosparql, beo, bot</t>
+          <t>geosparql, wgs84_pos, bot</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>geosparql, beo, bot</t>
+          <t>geosparql, wgs84_pos, bot</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -17853,12 +17841,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>dc, dcterms, wgs84_pos, skos, vcard, foaf, pi, schema</t>
+          <t>dc, dcterms, skos, vcard, foaf, pi, beo, schema</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>dc, dcterms, wgs84_pos, skos, vcard, foaf, pi, schema</t>
+          <t>dc, dcterms, skos, vcard, foaf, pi, beo, schema</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -17919,10 +17907,10 @@
       </c>
       <c r="AV64" t="inlineStr"/>
       <c r="AW64" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="AX64" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr"/>
@@ -17968,7 +17956,7 @@
       <c r="BT64" t="inlineStr"/>
       <c r="BU64" t="inlineStr">
         <is>
-          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {geo: http://www.opengis.net/ont/geosparql#}, {wgs84_pos: http://www.w3.org/2003/01/geo/wgs84_pos#}, {skos: http://www.w3.org/2004/02/skos/core#}, {vcard: http://www.w3.org/2006/vcard/ns#}, {foaf: http://xmlns.com/foaf/0.1/}, {None: https://orcid.org/}, {pi: https://pi.pauwel.be/voc/}, {beo: https://pi.pauwel.be/voc/buildingelement#}, {schema: https://schema.org/}, {None: https://w3id.org/}, {bot: https://w3id.org/bot#}</t>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {geo: http://www.opengis.net/ont/geosparql#}, {geo: http://www.w3.org/2003/01/geo/wgs84_pos#}, {skos: http://www.w3.org/2004/02/skos/core#}, {vcard: http://www.w3.org/2006/vcard/ns#}, {foaf: http://xmlns.com/foaf/0.1/}, {None: https://orcid.org/}, {pi: https://pi.pauwel.be/voc/}, {beo: https://pi.pauwel.be/voc/buildingelement#}, {schema: https://schema.org/}, {None: https://w3id.org/}, {bot: https://w3id.org/bot#}</t>
         </is>
       </c>
       <c r="BV64" t="n">
@@ -19476,12 +19464,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>geosparql, beo, saref4bldg, bot</t>
+          <t>geosparql, saref4bldg, bot</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>geosparql, beo, saref4bldg, bot</t>
+          <t>geosparql, saref4bldg, bot</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -19491,12 +19479,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>dc, dcterms, pi</t>
+          <t>dc, dcterms, pi, beo</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>dc, dcterms, pi</t>
+          <t>dc, dcterms, pi, beo</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -20176,19 +20164,19 @@
         </is>
       </c>
       <c r="B73" t="b">
-        <v>0</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>File not found</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>fisa</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>fisa</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>fisa</t>
@@ -20199,10 +20187,14 @@
           <t>Fire Safety Ontology</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Fire Safety Ontology (FiSa)</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Fire Safety Ontology</t>
+          <t>Fire Safety Ontology (FiSa)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -20210,7 +20202,11 @@
           <t xml:space="preserve">FiSa enables the classification of buildings and its components based on fire safety considerations. FiSa establish a fire safety perspective for buildings utilizing a combination of building codes, technical regulations, guidelines, and semi-structured interviews with fire safety planners. </t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Die Fire Safety (Brandschutz)-Ontologie (FiSa) ermöglicht die Klassifizierung von Gebäuden und ihren Komponenten auf der Grundlage von Brandschutzerwägungen. FiSa legt eine Brandschutzperspektive für Gebäude fest, indem es eine Kombination aus Bauvorschriften, technischen Vorschriften, Richtlinien und halbstrukturierten Interviews mit Brandschutzplanern verwendet. Anschließend wurden die Erkenntnisse von Brandschutzexperten mit dem Wissen über die Gebäudeplanung aus anderen Bereichen, wie z. B. der Architektur, abgeglichen. Durch diese Zusammenarbeit und die Instanziierung von Gebäudedaten innerhalb der Ontologie wurden die Anforderungen an den baulichen Brandschutz aus den Vorschriften automatisch abgeleitet, indem mit gängigen Inferenzmaschinen eine automatische Prüfung der Einhaltung der Vorschriften simuliert wurde.</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">FiSa enables the classification of buildings and its components based on fire safety considerations. FiSa establish a fire safety perspective for buildings utilizing a combination of building codes, technical regulations, guidelines, and semi-structured interviews with fire safety planners. </t>
@@ -20219,21 +20215,31 @@
       <c r="M73" t="n">
         <v>2023</v>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
-        <v>2023</v>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
           <t xml:space="preserve">CC BY 4.0 </t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC BY 4.0 </t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -20241,7 +20247,11 @@
           <t>0.0.1</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0.0.1</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr">
         <is>
           <t>0.0.1</t>
@@ -20252,7 +20262,11 @@
           <t>bot</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>bot</t>
+        </is>
+      </c>
       <c r="Z73" t="inlineStr">
         <is>
           <t>bot</t>
@@ -20263,24 +20277,32 @@
           <t>ns, skos, dcterms, vann, swrl, swrla, swrlb</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>dcterms, vann, swrla, swrl, swrlb, skos</t>
+        </is>
+      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>ns, skos, dcterms, vann, swrl, swrla, swrlb</t>
+          <t>dcterms, vann, swrla, swrl, swrlb, skos</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
-      <c r="AE73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>https://purl.org/fisa, https://purl.org/fisa/0.0.1</t>
+        </is>
+      </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>https://purl.org/fisa#</t>
+          <t>https://purl.org/fisa#, https://purl.org/fisa/0.0.1</t>
         </is>
       </c>
       <c r="AG73" t="b">
         <v>1</v>
       </c>
       <c r="AH73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI73" t="b">
         <v>1</v>
@@ -20295,16 +20317,22 @@
       <c r="AM73" t="b">
         <v>1</v>
       </c>
-      <c r="AN73" t="inlineStr"/>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
       <c r="AO73" t="b">
         <v>1</v>
       </c>
-      <c r="AP73" t="inlineStr"/>
+      <c r="AP73" t="n">
+        <v>92.3</v>
+      </c>
       <c r="AQ73" t="inlineStr"/>
       <c r="AR73" t="b">
         <v>0</v>
       </c>
-      <c r="AS73" t="inlineStr"/>
+      <c r="AS73" t="b">
+        <v>0</v>
+      </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AU73" t="inlineStr"/>
       <c r="AV73" t="inlineStr"/>
@@ -20352,17 +20380,41 @@
       <c r="BN73" t="inlineStr"/>
       <c r="BO73" t="inlineStr"/>
       <c r="BP73" t="inlineStr"/>
-      <c r="BQ73" t="inlineStr"/>
-      <c r="BR73" t="inlineStr"/>
+      <c r="BQ73" t="inlineStr">
+        <is>
+          <t>Isabelle Fitkau, Timo Hartmann</t>
+        </is>
+      </c>
+      <c r="BR73" t="inlineStr">
+        <is>
+          <t>Isabelle Fitkau, Timo Hartmann</t>
+        </is>
+      </c>
       <c r="BS73" t="inlineStr"/>
       <c r="BT73" t="inlineStr"/>
-      <c r="BU73" t="inlineStr"/>
-      <c r="BV73" t="inlineStr"/>
-      <c r="BW73" t="inlineStr"/>
-      <c r="BX73" t="inlineStr"/>
-      <c r="BY73" t="inlineStr"/>
-      <c r="BZ73" t="inlineStr"/>
-      <c r="CA73" t="inlineStr"/>
+      <c r="BU73" t="inlineStr">
+        <is>
+          <t>{bot: https://w3id.org/bot#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {dcterms: http://purl.org/dc/terms/}, {vann: http://purl.org/vocab/vann/}, {swrla: http://swrl.stanford.edu/ontologies/3.3/swrla.owl#}, {None: http://www.systemsEngineering.org/isabellefitkau/fisa.owl#}, {swrl: http://www.w3.org/2003/11/swrl#}, {swrlb: http://www.w3.org/2003/11/swrlb#}, {skos: http://www.w3.org/2004/02/skos/core#}</t>
+        </is>
+      </c>
+      <c r="BV73" t="n">
+        <v>291</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>291</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>49</v>
+      </c>
+      <c r="BY73" t="n">
+        <v>49</v>
+      </c>
+      <c r="BZ73" t="n">
+        <v>82</v>
+      </c>
+      <c r="CA73" t="n">
+        <v>82</v>
+      </c>
       <c r="CB73" t="b">
         <v>1</v>
       </c>
@@ -20379,7 +20431,7 @@
         <v>3</v>
       </c>
       <c r="CG73" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="CH73" t="b">
         <v>1</v>
@@ -20388,10 +20440,10 @@
         <v>1</v>
       </c>
       <c r="CJ73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -20748,12 +20800,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>dot, hmo, beo</t>
+          <t>dot, hmo</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>dot, hmo, beo</t>
+          <t>dot, hmo</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -20763,12 +20815,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>swrl, swrla, swrlb, terms</t>
+          <t>swrl, swrla, swrlb, terms, beo</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>swrl, swrla, swrlb, terms</t>
+          <t>swrl, swrla, swrlb, terms, beo</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr"/>
@@ -22153,12 +22205,12 @@
       </c>
       <c r="BS80" t="inlineStr">
         <is>
-          <t>na2a9af158b354639b43df31140a1ff5eb1</t>
+          <t>n37005061705f4b55a5e8034af243feb3b1</t>
         </is>
       </c>
       <c r="BT80" t="inlineStr">
         <is>
-          <t>na2a9af158b354639b43df31140a1ff5eb1</t>
+          <t>n37005061705f4b55a5e8034af243feb3b1</t>
         </is>
       </c>
       <c r="BU80" t="inlineStr">
@@ -22495,12 +22547,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>mat, beo, bot</t>
+          <t>mat, bot</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>mat, beo, bot</t>
+          <t>mat, bot</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -22510,12 +22562,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>pi, beo</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>pi</t>
+          <t>pi, beo</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr"/>
@@ -22782,12 +22834,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>mat, beo, saref, dot</t>
+          <t>mat, saref, dot</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>mat, beo, saref, dot</t>
+          <t>mat, saref, dot</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -22797,12 +22849,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>dcterms, vann, voaf, swrla, swrl, swrlb, foaf</t>
+          <t>dcterms, vann, voaf, swrla, swrl, swrlb, foaf, beo</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>dcterms, vann, voaf, swrla, swrl, swrlb, foaf</t>
+          <t>dcterms, vann, voaf, swrla, swrl, swrlb, foaf, beo</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr"/>
@@ -23502,22 +23554,22 @@
       <c r="BP85" t="inlineStr"/>
       <c r="BQ85" t="inlineStr">
         <is>
-          <t>nac05401ea87248369409910c8e914103b1</t>
+          <t>n5bcba6a0bde44477aca6b8c2244fcb18b1</t>
         </is>
       </c>
       <c r="BR85" t="inlineStr">
         <is>
-          <t>nac05401ea87248369409910c8e914103b1</t>
+          <t>n5bcba6a0bde44477aca6b8c2244fcb18b1</t>
         </is>
       </c>
       <c r="BS85" t="inlineStr">
         <is>
-          <t>nac05401ea87248369409910c8e914103b3</t>
+          <t>n5bcba6a0bde44477aca6b8c2244fcb18b3</t>
         </is>
       </c>
       <c r="BT85" t="inlineStr">
         <is>
-          <t>nac05401ea87248369409910c8e914103b3</t>
+          <t>n5bcba6a0bde44477aca6b8c2244fcb18b3</t>
         </is>
       </c>
       <c r="BU85" t="inlineStr">
@@ -24323,12 +24375,12 @@
       <c r="BP88" t="inlineStr"/>
       <c r="BQ88" t="inlineStr">
         <is>
-          <t>nc5cee9af1b5d4ec7b8cd43b648aa9990b1, nc5cee9af1b5d4ec7b8cd43b648aa9990b2</t>
+          <t>n098be0bab3ff45bd8a5dfa29cbe15bb0b1, n098be0bab3ff45bd8a5dfa29cbe15bb0b2</t>
         </is>
       </c>
       <c r="BR88" t="inlineStr">
         <is>
-          <t>nc5cee9af1b5d4ec7b8cd43b648aa9990b1, nc5cee9af1b5d4ec7b8cd43b648aa9990b2</t>
+          <t>n098be0bab3ff45bd8a5dfa29cbe15bb0b1, n098be0bab3ff45bd8a5dfa29cbe15bb0b2</t>
         </is>
       </c>
       <c r="BS88" t="inlineStr"/>
@@ -25453,12 +25505,12 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>loin, tempo</t>
+          <t>loin, tempo, ontobpr</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>loin, tempo</t>
+          <t>loin, tempo, ontobpr</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr"/>
@@ -25508,22 +25560,22 @@
       <c r="BP92" t="inlineStr"/>
       <c r="BQ92" t="inlineStr">
         <is>
-          <t>n4a9665ea5e534cf0a365d8ba65265cd5b3, n4a9665ea5e534cf0a365d8ba65265cd5b5</t>
+          <t>n54f7668b76494bdb886e42456221ae6db3, n54f7668b76494bdb886e42456221ae6db5</t>
         </is>
       </c>
       <c r="BR92" t="inlineStr">
         <is>
-          <t>n4a9665ea5e534cf0a365d8ba65265cd5b3, n4a9665ea5e534cf0a365d8ba65265cd5b5</t>
+          <t>n54f7668b76494bdb886e42456221ae6db3, n54f7668b76494bdb886e42456221ae6db5</t>
         </is>
       </c>
       <c r="BS92" t="inlineStr">
         <is>
-          <t>n4a9665ea5e534cf0a365d8ba65265cd5b7</t>
+          <t>n54f7668b76494bdb886e42456221ae6db7</t>
         </is>
       </c>
       <c r="BT92" t="inlineStr">
         <is>
-          <t>n4a9665ea5e534cf0a365d8ba65265cd5b7</t>
+          <t>n54f7668b76494bdb886e42456221ae6db7</t>
         </is>
       </c>
       <c r="BU92" t="inlineStr">
@@ -25587,13 +25639,9 @@
         </is>
       </c>
       <c r="B93" t="b">
-        <v>0</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>File not found</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>jup</t>
@@ -25661,29 +25709,43 @@
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr"/>
       <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>n07e847cd958c4e1ea71ea1e1415196feb1</t>
+        </is>
+      </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>http://w3id.org/charta77/jup</t>
+          <t>http://w3id.org/charta77/jup, n07e847cd958c4e1ea71ea1e1415196feb1</t>
         </is>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI93" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AI93" t="b">
+        <v>1</v>
+      </c>
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
       <c r="AM93" t="inlineStr"/>
-      <c r="AN93" t="inlineStr"/>
-      <c r="AO93" t="inlineStr"/>
-      <c r="AP93" t="inlineStr"/>
+      <c r="AN93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ93" t="inlineStr"/>
       <c r="AR93" t="b">
         <v>0</v>
       </c>
-      <c r="AS93" t="inlineStr"/>
+      <c r="AS93" t="b">
+        <v>0</v>
+      </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AU93" t="inlineStr"/>
       <c r="AV93" t="inlineStr"/>
@@ -25731,13 +25793,29 @@
       <c r="BR93" t="inlineStr"/>
       <c r="BS93" t="inlineStr"/>
       <c r="BT93" t="inlineStr"/>
-      <c r="BU93" t="inlineStr"/>
-      <c r="BV93" t="inlineStr"/>
-      <c r="BW93" t="inlineStr"/>
-      <c r="BX93" t="inlineStr"/>
-      <c r="BY93" t="inlineStr"/>
-      <c r="BZ93" t="inlineStr"/>
-      <c r="CA93" t="inlineStr"/>
+      <c r="BU93" t="inlineStr">
+        <is>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {None: http://linkedgeodata.org/meta/}, {None: http://linkedgeodata.org/ontology/}, {None: http://linkedgeodata.org/ontology/ATM/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AbandonedRailway/key/railway/value/}, {None: http://linkedgeodata.org/ontology/AbandonedStation/key/railway/value/}, {None: http://linkedgeodata.org/ontology/Abbey/key/historic/value/}, {None: http://linkedgeodata.org/ontology/AccountantOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/Adit/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/AdministrativeBoundary/key/boundary/value/}, {None: http://linkedgeodata.org/ontology/AdministrativeOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/AdultShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Advertisement/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Advertising/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AerialwayGoods/key/aerialway/value/}, {None: http://linkedgeodata.org/ontology/AerialwayStation/key/aerialway/value/}, {None: http://linkedgeodata.org/ontology/Agrarian/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AgriculturalEnginesCraft/key/craft/value/}, {None: http://linkedgeodata.org/ontology/AirFill/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Airplane/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Airport/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/Airport/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AirportField/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/AirportGate/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/AirportTaxiway/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/AirportTerminal/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/AirportTower/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/AlcoholShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Alley/key/service/value/}, {None: http://linkedgeodata.org/ontology/Allotments/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Alm/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AlpineHut/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/Ambulance/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AmbulanceStation/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AmbulanceStation/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/Amenity/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AnimalShelter/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/AnimalShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AnimalsShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AnimeShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Antenna/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/AntiqueShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AntiquesShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AntiquitiesShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/ApartmentBuilding/key/building/value/}, {None: http://linkedgeodata.org/ontology/Apparel/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Appliance/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Appliances/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Apron/key/aeroway/value/}, {None: http://linkedgeodata.org/ontology/Aqueduct/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/ArchaeologicalSite/key/historic/value/}, {None: http://linkedgeodata.org/ontology/ArchitectOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/ArtGallery/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/ArtGalleryShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/ArtShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/ArtSupplies/key/shop/value/}, {None: http://linkedgeodata.org/ontology/ArtsCentre/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Artwork/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Artwork/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/Atm/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Attraction/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/AudioVideoShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Audiologist/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AutoPartsShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AutoRepair/key/shop/value/}, {None: http://linkedgeodata.org/ontology/AutomotiveShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BabyGoodsShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BabyHatch/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BabyShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BagsShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Baisschool/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bakery/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bakery/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Bandstand/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bandstand/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Bank%2Catm/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bank%3Batm/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bank/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bar/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Barbeque/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Barber/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Barfusspfad/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Barracks/key/military/value/}, {None: http://linkedgeodata.org/ontology/Basin/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/BasketMaker/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Bathroom/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BathroomFurnishingShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Battlefield/key/historic/value/}, {None: http://linkedgeodata.org/ontology/Bay/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Bbq/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Beach/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Beach/key/natural/value/}, {None: http://linkedgeodata.org/ontology/BeachResort/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Beacon/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Beautician/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BeautySalon/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BeautyShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BedAndBreakfast/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/BedShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Bedrock/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Beekeeper/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Bench/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Betting/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BeverageMarket/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BicycleLockers/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BicycleParking/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BicycleRental/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BicycleRoute/key/route/value/}, {None: http://linkedgeodata.org/ontology/BicycleShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Biergarten/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Billboard/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Bingo/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/BirdHide/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Biwak/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/Blacksmith/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Block/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/BoatRental/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Boatbuilder/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Boatyard/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/Bollard/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/BookShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Bookbinder/key/craft/value/}, {None: http://linkedgeodata.org/ontology/BookmakerShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BookmakersShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BooksShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/BorderControl/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BorderControl/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/Borderstone/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/BoundaryForest/key/boundary/value/}, {None: http://linkedgeodata.org/ontology/BoundaryMarker/key/boundary/value/}, {None: http://linkedgeodata.org/ontology/BoundaryMarker/key/historic/value/}, {None: http://linkedgeodata.org/ontology/BoundaryStone/key/historic/value/}, {None: http://linkedgeodata.org/ontology/Boutique/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Brewery/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Brewery/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Bridge+pier/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Bridge+site/key/historic/value/}, {None: http://linkedgeodata.org/ontology/Bridge/key/railway/value/}, {None: http://linkedgeodata.org/ontology/Bridleway/key/highway/value/}, {None: http://linkedgeodata.org/ontology/Briefkasten/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Brothel/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Brownfield/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Bts/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BufferStop/key/railway/value/}, {None: http://linkedgeodata.org/ontology/Building/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Building/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingBarn/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingBuilding/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingBunker/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingCabin/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingChapel/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingChurch/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingCommercial/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingDormitory/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingEntrance/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BuildingEntrance/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingFarm/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingGarage/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingHall/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingHospital/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingHouse/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingHut/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingKiosk/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingMonastery/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingNo/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingOffice/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingResidential/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingRetail/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingSchool/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingTower/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingUniversity/key/building/value/}, {None: http://linkedgeodata.org/ontology/BuildingUnknown/key/building/value/}, {None: http://linkedgeodata.org/ontology/Bump/key/traffic_calming/value/}, {None: http://linkedgeodata.org/ontology/BureauDeChange/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BusGuideway/key/highway/value/}, {None: http://linkedgeodata.org/ontology/BusRoute/key/route/value/}, {None: http://linkedgeodata.org/ontology/BusStation/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BusStop/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/BusStop/key/highway/value/}, {None: http://linkedgeodata.org/ontology/Butcher/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Butchers/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Byway/key/highway/value/}, {None: http://linkedgeodata.org/ontology/CableCar/key/aerialway/value/}, {None: http://linkedgeodata.org/ontology/CableDistributionCabinet/key/power/value/}, {None: http://linkedgeodata.org/ontology/Cafe/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Cairn/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Camera/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CameraShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CampSite/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/CampingOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/Campsite/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Canal/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/CandyShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Cape/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Car%3BcarRepair/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CarDealer/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CarParts/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CarRental/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CarRepair/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CarRepairShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CarSharing/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CarShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CarWash/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CarWash/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CaravanSite/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/CardsShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CareHome/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Carpenter/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Carpenter/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Carpet/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CarpetLayer/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Carpets/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Casino/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Casino/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Castle/key/historic/value/}, {None: http://linkedgeodata.org/ontology/Catalogue/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Catere/key/craft/value/}, {None: http://linkedgeodata.org/ontology/CattleGrid/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/Cave/key/natural/value/}, {None: http://linkedgeodata.org/ontology/CaveEntrance/key/natural/value/}, {None: http://linkedgeodata.org/ontology/CellPhones/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Cemetery/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Cemetery/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Centre/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Ceramics/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Chain/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/ChairLift/key/aerialway/value/}, {None: http://linkedgeodata.org/ontology/Chalet/key/tourism/value/}, {None: http://linkedgeodata.org/ontology/Chandler/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Channel/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Chapel/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Charity/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CharityShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Cheese/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Chemist/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Chicane/key/traffic_calming/value/}, {None: http://linkedgeodata.org/ontology/ChildCare/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Chimney/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Chiropractor/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Chocolate/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Choker/key/traffic_calming/value/}, {None: http://linkedgeodata.org/ontology/Church/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/ChurchHall/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Cinema/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CircuitBreaker/key/power/value/}, {None: http://linkedgeodata.org/ontology/City/key/place/value/}, {None: http://linkedgeodata.org/ontology/CityGate/key/historic/value/}, {None: http://linkedgeodata.org/ontology/CityLimit/key/boundary/value/}, {None: http://linkedgeodata.org/ontology/CityWall/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/CitymapPost/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CivilBoundary/key/boundary/value/}, {None: http://linkedgeodata.org/ontology/Cliff/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Clinic/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Clock/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Clockmaker/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Closed/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Clothes%3A+women/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Clothes%3Awomen/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Clothes/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Clothing/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Club/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Club/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/ClubHouse/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Clubhouse/key/building/value/}, {None: http://linkedgeodata.org/ontology/Coastline/key/natural/value/}, {None: http://linkedgeodata.org/ontology/CoffeeShop/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CoffeeShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Col/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Collapsed/key/building/value/}, {None: http://linkedgeodata.org/ontology/College/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Commercial/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CommercialLanduse/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Common/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Communication/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Communications/key/shop/value/}, {None: http://linkedgeodata.org/ontology/CommunicationsTower/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/CommunicationsTransponder/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/CommunityCentre/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CommunityHall/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Company/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CompanyOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/Computer/key/shop/value/}, {None: http://linkedgeodata.org/ontology/ConcertHall/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Condos/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Confectionery/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Confectionery/key/shop/value/}, {None: http://linkedgeodata.org/ontology/ConferenceCentre/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Construction/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/ConstructionLanduse/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/ConstructionShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Consulate/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Continent/key/place/value/}, {None: http://linkedgeodata.org/ontology/Convenience/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Copyshop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Cosmetics/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Country/key/place/value/}, {None: http://linkedgeodata.org/ontology/County/key/place/value/}, {None: http://linkedgeodata.org/ontology/Courthouse/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/CoveredReservoir/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Craft/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Crafts/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Crane/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Crater/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Crematorium/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Cross/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Cushion/key/traffic_calming/value/}, {None: http://linkedgeodata.org/ontology/Customs/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Cutline/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/CycleBarrier/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/Cycleway/key/highway/value/}, {None: http://linkedgeodata.org/ontology/CyclewayLane/key/cycleway/value/}, {None: http://linkedgeodata.org/ontology/CyclewayOpposite/key/cycleway/value/}, {None: http://linkedgeodata.org/ontology/CyclewayOppositeLane/key/cycleway/value/}, {None: http://linkedgeodata.org/ontology/CyclewayOppositeTrack/key/cycleway/value/}, {None: http://linkedgeodata.org/ontology/CyclewayTrack/key/cycleway/value/}, {None: http://linkedgeodata.org/ontology/Dairy/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Dam/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/Dance/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/DangerArea/key/military/value/}, {None: http://linkedgeodata.org/ontology/Daycare/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DeadPub/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Decoration/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Deli/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Delicatessen/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Dentist/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DepartmentStore/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Dept/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Depth/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/Derestricted+speed+limit/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Design/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Detached/key/building/value/}, {None: http://linkedgeodata.org/ontology/DetourRoute/key/route/value/}, {None: http://linkedgeodata.org/ontology/Discount/key/shop/value/}, {None: http://linkedgeodata.org/ontology/DisusedPub/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DisusedRailway/key/railway/value/}, {None: http://linkedgeodata.org/ontology/DisusedStation/key/railway/value/}, {None: http://linkedgeodata.org/ontology/Ditch/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/DitchBarrier/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/DiveCenter/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DiveCentre/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Diy/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Dock/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/Doctor/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Doctors/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DogBin/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DogPark/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/DogWaste/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Doityourself/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Dollar/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Dormitory/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Downhill+Terminal/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/DragLift/key/aerialway/value/}, {None: http://linkedgeodata.org/ontology/Drain/key/waterway/value/}, {None: http://linkedgeodata.org/ontology/Dressmaker/key/craft/value/}, {None: http://linkedgeodata.org/ontology/DrinkingWater/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DriveWay/key/service/value/}, {None: http://linkedgeodata.org/ontology/DrivingSchool/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/DrivingSchoolShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Drugstore/key/shop/value/}, {None: http://linkedgeodata.org/ontology/DryCleaning/key/shop/value/}, {None: http://linkedgeodata.org/ontology/EducationalInstitutionOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/Electrician/key/craft/value/}, {None: http://linkedgeodata.org/ontology/Electrician/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Electronics/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Elevator/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Embassy/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/EmergencyAccessPoint/key/highway/value/}, {None: http://linkedgeodata.org/ontology/EmergencyPhone/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/EmergencyPhone/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/EmergencySiren/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/EmergencyTelephone/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/EmploymentAgencyOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/Empty/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Entrance/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Entrance/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/Entry/key/building/value/}, {None: http://linkedgeodata.org/ontology/EnvironmentalHazard/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Estanco/key/shop/value/}, {None: http://linkedgeodata.org/ontology/EstateAgent/key/shop/value/}, {None: http://linkedgeodata.org/ontology/EstateAgentOffice/key/office/value/}, {None: http://linkedgeodata.org/ontology/EvCharging/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Fabric/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fabrics/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Factory/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Fairtrade/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Farm/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Farm/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Farm/key/place/value/}, {None: http://linkedgeodata.org/ontology/FarmShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Farmland/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Farmyard/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Fashion/key/shop/value/}, {None: http://linkedgeodata.org/ontology/FastFood/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Feature/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Fell/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Fen/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Fence/key/barrier/value/}, {None: http://linkedgeodata.org/ontology/FerryRoute/key/route/value/}, {None: http://linkedgeodata.org/ontology/FerryTerminal/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Financial/key/shop/value/}, {None: http://linkedgeodata.org/ontology/FireBeater/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FireExtinguisher/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/FireFlapper/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/FireHose/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/FireHydrant/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FireHydrant/key/emergency/value/}, {None: http://linkedgeodata.org/ontology/FireStation/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Fireplace/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FirstAid/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Fish/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fishing/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/FishingShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fishmonger/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fitness+trail/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/Fitness/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/FitnessCentre/key/leisure/value/}, {None: http://linkedgeodata.org/ontology/FitnessShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fjord/key/natural/value/}, {None: http://linkedgeodata.org/ontology/Flagpole/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Flats/key/building/value/}, {None: http://linkedgeodata.org/ontology/Flooring/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Florist/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FloristShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Flowers/key/shop/value/}, {None: http://linkedgeodata.org/ontology/FolkArt/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Food/key/shop/value/}, {None: http://linkedgeodata.org/ontology/FoodCourt/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FootShower/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Footway/key/highway/value/}, {None: http://linkedgeodata.org/ontology/Forest/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Forester/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Fort/key/historic/value/}, {None: http://linkedgeodata.org/ontology/Fortress/key/building/value/}, {None: http://linkedgeodata.org/ontology/Foto/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fountain/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/Fraternity/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FrozenFoodShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fruit/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Fuel%3BcarWash/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FuelStation/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FuneralDirectors/key/shop/value/}, {None: http://linkedgeodata.org/ontology/FuneralHome/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/FunicularRailway/key/railway/value/}, {None: http://linkedgeodata.org/ontology/Furniture/key/shop/value/}, {None: http://linkedgeodata.org/ontology/GagingStation/key/man_made/value/}, {None: http://linkedgeodata.org/ontology/Gallery/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/GalleryShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Gambling/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/GamblingShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Games/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Garage/key/amenity/value/}, {None: http://linkedgeodata.org/ontology/GarageShop/key/shop/value/}, {None: http://linkedgeodata.org/ontology/Garages/key/landuse/value/}, {None: http://linkedgeodata.org/ontology/Garbage/key/amenity/value/},</t>
+        </is>
+      </c>
+      <c r="BV93" t="n">
+        <v>1200</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>1200</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>0</v>
+      </c>
       <c r="CB93" t="b">
         <v>0</v>
       </c>
@@ -25751,7 +25829,7 @@
         <v>0</v>
       </c>
       <c r="CF93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CG93" t="n">
         <v>0</v>
@@ -26529,22 +26607,22 @@
       <c r="BP96" t="inlineStr"/>
       <c r="BQ96" t="inlineStr">
         <is>
-          <t>n8332b24e70514fb1a43c2bb4856209fdb3, n8332b24e70514fb1a43c2bb4856209fdb5</t>
+          <t>nb979c03628674397801d9c09010bcfcab3, nb979c03628674397801d9c09010bcfcab5</t>
         </is>
       </c>
       <c r="BR96" t="inlineStr">
         <is>
-          <t>n8332b24e70514fb1a43c2bb4856209fdb3, n8332b24e70514fb1a43c2bb4856209fdb5</t>
+          <t>nb979c03628674397801d9c09010bcfcab3, nb979c03628674397801d9c09010bcfcab5</t>
         </is>
       </c>
       <c r="BS96" t="inlineStr">
         <is>
-          <t>n8332b24e70514fb1a43c2bb4856209fdb7</t>
+          <t>nb979c03628674397801d9c09010bcfcab7</t>
         </is>
       </c>
       <c r="BT96" t="inlineStr">
         <is>
-          <t>n8332b24e70514fb1a43c2bb4856209fdb7</t>
+          <t>nb979c03628674397801d9c09010bcfcab7</t>
         </is>
       </c>
       <c r="BU96" t="inlineStr">
@@ -27404,12 +27482,12 @@
       </c>
       <c r="BQ99" t="inlineStr">
         <is>
-          <t>nf020169d3a0547808d6d825c1f8598edb1</t>
+          <t>nb5a597b7606446a3b2f525ea581a3106b1</t>
         </is>
       </c>
       <c r="BR99" t="inlineStr">
         <is>
-          <t>nf020169d3a0547808d6d825c1f8598edb1</t>
+          <t>nb5a597b7606446a3b2f525ea581a3106b1</t>
         </is>
       </c>
       <c r="BS99" t="inlineStr"/>
@@ -28306,7 +28384,7 @@
       <c r="AP103" t="inlineStr"/>
       <c r="AQ103" t="inlineStr"/>
       <c r="AR103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="inlineStr"/>
@@ -30426,12 +30504,12 @@
       <c r="BP111" t="inlineStr"/>
       <c r="BQ111" t="inlineStr">
         <is>
-          <t>ne0b27994e94a45789978947597bcb413b1, ne0b27994e94a45789978947597bcb413b2</t>
+          <t>nc8c0645f3fbc46db9d1902f8d63bba02b1, nc8c0645f3fbc46db9d1902f8d63bba02b2</t>
         </is>
       </c>
       <c r="BR111" t="inlineStr">
         <is>
-          <t>ne0b27994e94a45789978947597bcb413b1, ne0b27994e94a45789978947597bcb413b2</t>
+          <t>nc8c0645f3fbc46db9d1902f8d63bba02b1, nc8c0645f3fbc46db9d1902f8d63bba02b2</t>
         </is>
       </c>
       <c r="BS111" t="inlineStr"/>
@@ -30499,11 +30577,7 @@
       <c r="B112" t="b">
         <v>1</v>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>'preferred_prefix'</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>ph</t>
@@ -30564,7 +30638,11 @@
           <t>4.0.0</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>4.0.0</t>
+        </is>
+      </c>
       <c r="W112" t="inlineStr">
         <is>
           <t>4.0.0</t>
@@ -30574,10 +30652,22 @@
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr"/>
-      <c r="AC112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>phIct, phScience, phIoT</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>phIct, phScience, phIoT</t>
+        </is>
+      </c>
       <c r="AD112" t="inlineStr"/>
-      <c r="AE112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>https://project-haystack.org/def/ph/4.0.0</t>
+        </is>
+      </c>
       <c r="AF112" t="inlineStr">
         <is>
           <t>https://project-haystack.org/def/ph/4.0.0#</t>
@@ -30587,10 +30677,10 @@
         <v>1</v>
       </c>
       <c r="AH112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ112" t="b">
         <v>1</v>
@@ -30602,9 +30692,15 @@
       <c r="AM112" t="b">
         <v>1</v>
       </c>
-      <c r="AN112" t="inlineStr"/>
-      <c r="AO112" t="inlineStr"/>
-      <c r="AP112" t="inlineStr"/>
+      <c r="AN112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO112" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>98.8</v>
+      </c>
       <c r="AQ112" t="inlineStr"/>
       <c r="AR112" t="b">
         <v>0</v>
@@ -30663,15 +30759,31 @@
       <c r="BR112" t="inlineStr"/>
       <c r="BS112" t="inlineStr"/>
       <c r="BT112" t="inlineStr"/>
-      <c r="BU112" t="inlineStr"/>
-      <c r="BV112" t="inlineStr"/>
-      <c r="BW112" t="inlineStr"/>
-      <c r="BX112" t="inlineStr"/>
-      <c r="BY112" t="inlineStr"/>
-      <c r="BZ112" t="inlineStr"/>
-      <c r="CA112" t="inlineStr"/>
+      <c r="BU112" t="inlineStr">
+        <is>
+          <t>{rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {owl: http://www.w3.org/2002/07/owl#}, {phIct: https://project-haystack.org/def/phIct/4.0.0#}, {phScience: https://project-haystack.org/def/phScience/4.0.0#}, {phIoT: https://project-haystack.org/def/phIoT/4.0.0#}</t>
+        </is>
+      </c>
+      <c r="BV112" t="n">
+        <v>562</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>562</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>29</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>29</v>
+      </c>
       <c r="CB112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC112" t="b">
         <v>0</v>
@@ -30680,13 +30792,13 @@
         <v>0</v>
       </c>
       <c r="CE112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF112" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG112" t="n">
         <v>2</v>
-      </c>
-      <c r="CG112" t="n">
-        <v>1</v>
       </c>
       <c r="CH112" t="b">
         <v>1</v>
@@ -31376,23 +31488,23 @@
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>beo, dot</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>beo, dot</t>
+          <t>dot</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>dc, dcterms, vann, schema, foaf, pi</t>
+          <t>dc, dcterms, vann, schema, foaf, pi, beo</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>dc, dcterms, vann, schema, foaf, pi</t>
+          <t>dc, dcterms, vann, schema, foaf, pi, beo</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -33194,13 +33306,7 @@
       <c r="B122" t="b">
         <v>1</v>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>at line 262 of &lt;&gt;:
-Bad syntax (Prefix "xs:" not bound) at ^ in:
-"...b'alysis ,\r\nsao:StreamData ,\r\nsao:StreamEvent ;\r\n\r\nrdfs:range '^b'xs:dateTimeStamp .\r\n\r\n\r\n\r\n###  http://purl.oclc.org/NET/UNIS'..."</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>sao</t>
@@ -33262,17 +33368,37 @@
           <t>ssn</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr"/>
-      <c r="Z122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>wgs84_pos</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>wgs84_pos</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>prov, tl</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr"/>
-      <c r="AC122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>dc, tl, DUL, muo, ssn, xs, prov, event</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>dc, tl, DUL, muo, ssn, xs, prov, event</t>
+        </is>
+      </c>
       <c r="AD122" t="inlineStr"/>
-      <c r="AE122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>http://iot.ee.surrey.ac.uk/citypulse/ontologies/sao/sao#</t>
+        </is>
+      </c>
       <c r="AF122" t="inlineStr">
         <is>
           <t>http://iot.ee.surrey.ac.uk/citypulse/ontologies/sao/sao#</t>
@@ -33282,10 +33408,10 @@
         <v>1</v>
       </c>
       <c r="AH122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ122" t="b">
         <v>1</v>
@@ -33297,9 +33423,15 @@
       <c r="AM122" t="b">
         <v>0</v>
       </c>
-      <c r="AN122" t="inlineStr"/>
-      <c r="AO122" t="inlineStr"/>
-      <c r="AP122" t="inlineStr"/>
+      <c r="AN122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>47.7</v>
+      </c>
       <c r="AQ122" t="inlineStr"/>
       <c r="AR122" t="b">
         <v>0</v>
@@ -33311,10 +33443,10 @@
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr"/>
       <c r="AW122" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="AX122" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr"/>
@@ -33358,30 +33490,46 @@
       <c r="BR122" t="inlineStr"/>
       <c r="BS122" t="inlineStr"/>
       <c r="BT122" t="inlineStr"/>
-      <c r="BU122" t="inlineStr"/>
-      <c r="BV122" t="inlineStr"/>
-      <c r="BW122" t="inlineStr"/>
-      <c r="BX122" t="inlineStr"/>
-      <c r="BY122" t="inlineStr"/>
-      <c r="BZ122" t="inlineStr"/>
-      <c r="CA122" t="inlineStr"/>
+      <c r="BU122" t="inlineStr">
+        <is>
+          <t>{dc: http://purl.org/dc/terms/}, {tl: http://purl.org/NET/c4dm/timeline.owl#}, {DUL: http://www.loa-cnr.it/ontologies/DUL.owl#}, {geo: http://www.w3.org/2003/01/geo/wgs84_pos#}, {muo: http://purl.oclc.org/NET/muo/muo#}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {ssn: http://purl.oclc.org/NET/ssnx/ssn#}, {xs: http://www.w3.org/2001/XMLSchema#}, {prov: http://www.w3.org/ns/prov#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {event: http://purl.org/NET/c4dm/event.owl#}</t>
+        </is>
+      </c>
+      <c r="BV122" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>16</v>
+      </c>
       <c r="CB122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CC122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD122" t="b">
         <v>0</v>
       </c>
       <c r="CE122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CG122" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="CH122" t="b">
         <v>1</v>
@@ -39839,12 +39987,12 @@
       <c r="BP144" t="inlineStr"/>
       <c r="BQ144" t="inlineStr">
         <is>
-          <t>n232e030ebdcc47bc99634633114ca761b1</t>
+          <t>n0b9618d3f0cd48fe9565ffca3abac15fb1</t>
         </is>
       </c>
       <c r="BR144" t="inlineStr">
         <is>
-          <t>n232e030ebdcc47bc99634633114ca761b1</t>
+          <t>n0b9618d3f0cd48fe9565ffca3abac15fb1</t>
         </is>
       </c>
       <c r="BS144" t="inlineStr"/>
@@ -40132,12 +40280,12 @@
       <c r="BP145" t="inlineStr"/>
       <c r="BQ145" t="inlineStr">
         <is>
-          <t>n256b4ccd1eed4fa4bbb236f52b9b3dd0b1</t>
+          <t>n9aa830d03df7498195dd3130c1ea25b0b1</t>
         </is>
       </c>
       <c r="BR145" t="inlineStr">
         <is>
-          <t>n256b4ccd1eed4fa4bbb236f52b9b3dd0b1</t>
+          <t>n9aa830d03df7498195dd3130c1ea25b0b1</t>
         </is>
       </c>
       <c r="BS145" t="inlineStr"/>
@@ -40707,22 +40855,22 @@
       </c>
       <c r="BQ147" t="inlineStr">
         <is>
-          <t>nbae269f04bf64b89af05f70077a8af3bb1, nbae269f04bf64b89af05f70077a8af3bb3, nbae269f04bf64b89af05f70077a8af3bb5, nbae269f04bf64b89af05f70077a8af3bb7</t>
+          <t>n4ebc872c4d7a43c5b2c2c5764f5d77e4b1, n4ebc872c4d7a43c5b2c2c5764f5d77e4b3, n4ebc872c4d7a43c5b2c2c5764f5d77e4b5, n4ebc872c4d7a43c5b2c2c5764f5d77e4b7</t>
         </is>
       </c>
       <c r="BR147" t="inlineStr">
         <is>
-          <t>nbae269f04bf64b89af05f70077a8af3bb1, nbae269f04bf64b89af05f70077a8af3bb3, nbae269f04bf64b89af05f70077a8af3bb5, nbae269f04bf64b89af05f70077a8af3bb7</t>
+          <t>n4ebc872c4d7a43c5b2c2c5764f5d77e4b1, n4ebc872c4d7a43c5b2c2c5764f5d77e4b3, n4ebc872c4d7a43c5b2c2c5764f5d77e4b5, n4ebc872c4d7a43c5b2c2c5764f5d77e4b7</t>
         </is>
       </c>
       <c r="BS147" t="inlineStr">
         <is>
-          <t>nbae269f04bf64b89af05f70077a8af3bb9</t>
+          <t>n4ebc872c4d7a43c5b2c2c5764f5d77e4b9</t>
         </is>
       </c>
       <c r="BT147" t="inlineStr">
         <is>
-          <t>nbae269f04bf64b89af05f70077a8af3bb9</t>
+          <t>n4ebc872c4d7a43c5b2c2c5764f5d77e4b9</t>
         </is>
       </c>
       <c r="BU147" t="inlineStr">
@@ -42073,8 +42221,16 @@
           <t>wgs84_pos</t>
         </is>
       </c>
-      <c r="Y153" t="inlineStr"/>
-      <c r="Z153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>wgs84_pos</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>wgs84_pos</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>time</t>
@@ -42082,12 +42238,12 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>time, wgs84_pos</t>
+          <t>time</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>time, wgs84_pos</t>
+          <t>time</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -42214,13 +42370,13 @@
         <v>1</v>
       </c>
       <c r="CC153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD153" t="b">
         <v>0</v>
       </c>
       <c r="CE153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF153" t="n">
         <v>2</v>
@@ -42968,12 +43124,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>sosa, ssn, saref, saref4city</t>
+          <t>wgs84_pos, sosa, ssn, saref, saref4city</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>sosa, ssn, saref, saref4city</t>
+          <t>wgs84_pos, sosa, ssn, saref, saref4city</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -42983,12 +43139,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>dc, dcterms, vann, schema, wgs84_pos, skos</t>
+          <t>dc, dcterms, vann, schema, skos</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>dc, dcterms, vann, schema, wgs84_pos, skos</t>
+          <t>dc, dcterms, vann, schema, skos</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr"/>
@@ -43114,7 +43270,7 @@
       </c>
       <c r="BU157" t="inlineStr">
         <is>
-          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {None: http://creativecommons.org/licenses/by/4.0/}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {vann: http://purl.org/vocab/vann/}, {schema: http://schema.org/}, {None: http://www.ontology-of-units-of-measure.org/resource/om-2/}, {wgs84_pos: http://www.w3.org/2003/01/geo/wgs84_pos#}, {skos: http://www.w3.org/2004/02/skos/core#}, {sosa: http://www.w3.org/ns/sosa/}, {ssn: http://www.w3.org/ns/ssn/}, {None: https://oeg.fi.upm.es/}, {saref: https://saref.etsi.org/core/}, {None: https://w3id.org/def/saref4city#}, {None: https://w3id.org/saref#}</t>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {None: http://creativecommons.org/licenses/by/4.0/}, {dc: http://purl.org/dc/elements/1.1/}, {dcterms: http://purl.org/dc/terms/}, {vann: http://purl.org/vocab/vann/}, {schema: http://schema.org/}, {None: http://www.ontology-of-units-of-measure.org/resource/om-2/}, {geo: http://www.w3.org/2003/01/geo/wgs84_pos#}, {skos: http://www.w3.org/2004/02/skos/core#}, {sosa: http://www.w3.org/ns/sosa/}, {ssn: http://www.w3.org/ns/ssn/}, {None: https://oeg.fi.upm.es/}, {saref: https://saref.etsi.org/core/}, {None: https://w3id.org/def/saref4city#}, {None: https://w3id.org/saref#}</t>
         </is>
       </c>
       <c r="BV157" t="n">
@@ -43169,7 +43325,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://w3.org/2003/01/geo/wgs84_pos#</t>
+          <t>https://www.w3.org/2003/01/geo/wgs84_pos#</t>
         </is>
       </c>
       <c r="B158" t="b">
@@ -43192,7 +43348,11 @@
           <t>WGS84 Geo Positioning: an RDF vocabulary</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>WGS84 Geo Positioning: an RDF vocabulary</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
           <t>WGS84 Geo Positioning: an RDF vocabulary</t>
@@ -43203,7 +43363,13 @@
           <t xml:space="preserve">This is a basic RDF vocabulary that provides the Semantic Web community with a namespace for representing lat(itude), long(itude) and other information about spatially-located things, using WGS84 as a reference datum. This vocabulary begins an exploration of the possibilities of representing mapping/location data in RDF, and does not attempt to address many of the issues covered in the professional GIS world, notably by the Open Geospatial Consortium (OGC). Instead, we provide just a few basic terms that can be used in RDF (eg. RSS 1.0 or FOAF documents) when there is a need to describe latitudes and longitudes. The motivation for using RDF as a carrier for lat/long info is RDF's capability for cross-domain data mixing. We can describe not only maps, but the entities that are positioned on the map. And we can use any relevant RDF vocabularies to do so, without the need for expensive pre-coordination, or for changes to a centrally maintained schema. </t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>A vocabulary for representing latitude, longitude and 
+ altitude information in the WGS84 geodetic reference datum. 
+ Version $Id: wgs84_pos.rdf,v 1.22 2009/04/20 15:00:30 timbl Exp $. See http://www.w3.org/2003/01/geo/ for more details.</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">This is a basic RDF vocabulary that provides the Semantic Web community with a namespace for representing lat(itude), long(itude) and other information about spatially-located things, using WGS84 as a reference datum. This vocabulary begins an exploration of the possibilities of representing mapping/location data in RDF, and does not attempt to address many of the issues covered in the professional GIS world, notably by the Open Geospatial Consortium (OGC). Instead, we provide just a few basic terms that can be used in RDF (eg. RSS 1.0 or FOAF documents) when there is a need to describe latitudes and longitudes. The motivation for using RDF as a carrier for lat/long info is RDF's capability for cross-domain data mixing. We can describe not only maps, but the entities that are positioned on the map. And we can use any relevant RDF vocabularies to do so, without the need for expensive pre-coordination, or for changes to a centrally maintained schema. </t>
@@ -43234,23 +43400,23 @@
       <c r="AA158" t="inlineStr"/>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>dc, wgs84_pos, foaf</t>
+          <t>dc, foaf</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>dc, wgs84_pos, foaf</t>
+          <t>dc, foaf</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>n594f25b238d84756a9d269ef4857e3bbb1</t>
+          <t>http://www.w3.org/2003/01/geo/wgs84_pos#</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>https://w3.org/2003/01/geo/wgs84_pos#, n594f25b238d84756a9d269ef4857e3bbb1</t>
+          <t>https://www.w3.org/2003/01/geo/wgs84_pos#</t>
         </is>
       </c>
       <c r="AG158" t="b">
@@ -43273,13 +43439,13 @@
         <v>1</v>
       </c>
       <c r="AN158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP158" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AQ158" t="inlineStr"/>
       <c r="AR158" t="b">
@@ -43288,16 +43454,24 @@
       <c r="AS158" t="b">
         <v>1</v>
       </c>
-      <c r="AT158" t="inlineStr"/>
-      <c r="AU158" t="inlineStr"/>
+      <c r="AT158" t="inlineStr">
+        <is>
+          <t>building, dtc, sao, th-weather, weat</t>
+        </is>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>building, dtc, sao, th-weather, weat</t>
+        </is>
+      </c>
       <c r="AV158" t="n">
         <v>30</v>
       </c>
       <c r="AW158" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AX158" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr"/>
@@ -43343,7 +43517,7 @@
       <c r="BT158" t="inlineStr"/>
       <c r="BU158" t="inlineStr">
         <is>
-          <t>{dc: http://purl.org/dc/elements/1.1/}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {wgs84_pos: http://www.w3.org/2003/01/geo/wgs84_pos#}, {foaf: http://xmlns.com/foaf/0.1/}</t>
+          <t>{dc: http://purl.org/dc/elements/1.1/}, {owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {foaf: http://xmlns.com/foaf/0.1/}</t>
         </is>
       </c>
       <c r="BV158" t="n">
@@ -43380,7 +43554,7 @@
         <v>2</v>
       </c>
       <c r="CG158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CH158" t="b">
         <v>0</v>
@@ -43646,6 +43820,261 @@
         <v>1</v>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://w3id.org/ontobpr#</t>
+        </is>
+      </c>
+      <c r="B160" t="b">
+        <v>1</v>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ontobpr</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>ontobpr</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ontobpr</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>OntoBPR: An ontological workflow for building permit review</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>OntoBPR: An ontological workflow for building permit review</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>OntoBPR: An ontological workflow for building permit review</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Building permitting is essential for ensuring the safety, sustainability, and societal alignment of construction projects. Despite interest from both practitioners and researchers, the process remains largely manual and fragmented. Ontologies offer a promising solution by managing complexity and enabling automation through semantic information, though current ontologies in the building permit domain are limited to specific aspects like building code checking. On the process level, the OntoBPR framework integrates multiple domain-specific ontologies for a seamless digital permitting process and provides a workflow to automate the lifecycle of the permit review. Therefore, it suggests integrating the submitted building application using standardized information containers. The paper explores how digital applications can be submitted, reviewed, verified for completeness, and forwarded to authorities, and how permit review results can be gathered to support decision-making and automate notification issuance, and it provides a demonstration in a case study. In conclusion, OntoBPR formalizes a multi-layered ontology that advances and aligns the partitioned building permit process and provides an adaptable framework to harmonize diverse legal, informatics, and procedural aspects.</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>To avoid a digital disruption in planning buildings and structures, this research presents a workflow in which building codes are represented as machine-readable knowledge graphs and ontologies as an integration to the building permit review procedure and the participation process. Therefore, the building permit process was analyzed, and possible applications of ontology-based knowledge representations are explored. An ontology-based building permit review (OntoBPR) is proposed, reusing two existing ontologies for modeling the permit review workflow for representing the building codes. The OntoBPR ontology extends the approach with a connection to Information Containers for linked Document Delivery (ICDD) that are used for submitting the building application, and the Shapes Constraint Language (SHACL) of which rules are generated from the building code knowledge graphs.</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Building permitting is essential for ensuring the safety, sustainability, and societal alignment of construction projects. Despite interest from both practitioners and researchers, the process remains largely manual and fragmented. Ontologies offer a promising solution by managing complexity and enabling automation through semantic information, though current ontologies in the building permit domain are limited to specific aspects like building code checking. On the process level, the OntoBPR framework integrates multiple domain-specific ontologies for a seamless digital permitting process and provides a workflow to automate the lifecycle of the permit review. Therefore, it suggests integrating the submitted building application using standardized information containers. The paper explores how digital applications can be submitted, reviewed, verified for completeness, and forwarded to authorities, and how permit review results can be gathered to support decision-making and automate notification issuance, and it provides a demonstration in a case study. In conclusion, OntoBPR formalizes a multi-layered ontology that advances and aligns the partitioned building permit process and provides an adaptable framework to harmonize diverse legal, informatics, and procedural aspects.</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>2022</v>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="n">
+        <v>2022</v>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>CC BY SA 4.0</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>CC BY SA 4.0</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+      <c r="W160" t="inlineStr"/>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>obpa, isoprops</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>isoprops</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>isoprops</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr"/>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>dc, vann, sh, schema, ct</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>dc, vann, sh, schema, ct</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>https://w3id.org/ontobpr, https://w3id.org/ontobpr#</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>https://w3id.org/ontobpr#</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI160" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ160" t="inlineStr"/>
+      <c r="AK160" t="inlineStr"/>
+      <c r="AL160" t="inlineStr"/>
+      <c r="AM160" t="inlineStr"/>
+      <c r="AN160" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO160" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="AQ160" t="inlineStr"/>
+      <c r="AR160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AU160" t="inlineStr"/>
+      <c r="AV160" t="inlineStr"/>
+      <c r="AW160" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr"/>
+      <c r="BA160" t="inlineStr"/>
+      <c r="BB160" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC160" t="inlineStr"/>
+      <c r="BD160" t="b">
+        <v>1</v>
+      </c>
+      <c r="BE160" t="inlineStr"/>
+      <c r="BF160" t="inlineStr"/>
+      <c r="BG160" t="inlineStr"/>
+      <c r="BH160" t="inlineStr">
+        <is>
+          <t>https://github.com/RUB-Informatik-im-Bauwesen/ontobpr; https://doi.org/10.1016/j.aei.2025.103369</t>
+        </is>
+      </c>
+      <c r="BI160" t="inlineStr"/>
+      <c r="BJ160" t="inlineStr">
+        <is>
+          <t>https://github.com/RUB-Informatik-im-Bauwesen/ontobpr; https://doi.org/10.1016/j.aei.2025.103369</t>
+        </is>
+      </c>
+      <c r="BK160" t="inlineStr">
+        <is>
+          <t>Planning Permission</t>
+        </is>
+      </c>
+      <c r="BL160" t="inlineStr"/>
+      <c r="BM160" t="inlineStr">
+        <is>
+          <t>Planning Permission</t>
+        </is>
+      </c>
+      <c r="BN160" t="inlineStr"/>
+      <c r="BO160" t="inlineStr"/>
+      <c r="BP160" t="inlineStr"/>
+      <c r="BQ160" t="inlineStr">
+        <is>
+          <t>ndb51cde82bf8445cb389b6311bab09f1b1, ndb51cde82bf8445cb389b6311bab09f1b2, ndb51cde82bf8445cb389b6311bab09f1b3, ndb51cde82bf8445cb389b6311bab09f1b4</t>
+        </is>
+      </c>
+      <c r="BR160" t="inlineStr">
+        <is>
+          <t>ndb51cde82bf8445cb389b6311bab09f1b1, ndb51cde82bf8445cb389b6311bab09f1b2, ndb51cde82bf8445cb389b6311bab09f1b3, ndb51cde82bf8445cb389b6311bab09f1b4</t>
+        </is>
+      </c>
+      <c r="BS160" t="inlineStr"/>
+      <c r="BT160" t="inlineStr"/>
+      <c r="BU160" t="inlineStr">
+        <is>
+          <t>{owl: http://www.w3.org/2002/07/owl#}, {rdf: http://www.w3.org/1999/02/22-rdf-syntax-ns#}, {xsd: http://www.w3.org/2001/XMLSchema#}, {rdfs: http://www.w3.org/2000/01/rdf-schema#}, {None: http://org.semanticweb.owlapi/error#}, {dc: http://purl.org/dc/elements/1.1/}, {vann: http://purl.org/vocab/vann/}, {sh: http://www.w3.org/ns/shacl#}, {None: https://creativecommons.org/licenses/by/4.0/}, {None: https://orcid.org/}, {schema: https://schema.org/}, {ct: https://standards.iso.org/iso/21597/-1/ed-1/en/Container#}, {isoprops: https://w3id.org/isoprops#}, {None: https://w3id.org/obpa#}, {None: https://www.inf.bi.ruhr-uni-bochum.de/iib/lehrstuhl/mitarbeiter/}, {None: https://www.linkedin.com/in/}, {None: https://www.uni-weimar.de/de/bau-und-umwelt/professuren/baubetrieb-und-bauverfahren/personen/sebastian-seiss-msc/}</t>
+        </is>
+      </c>
+      <c r="BV160" t="n">
+        <v>48</v>
+      </c>
+      <c r="BW160" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ160" t="n">
+        <v>15</v>
+      </c>
+      <c r="CA160" t="n">
+        <v>15</v>
+      </c>
+      <c r="CB160" t="b">
+        <v>1</v>
+      </c>
+      <c r="CC160" t="b">
+        <v>1</v>
+      </c>
+      <c r="CD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="CE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="CF160" t="n">
+        <v>3</v>
+      </c>
+      <c r="CG160" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="CH160" t="b">
+        <v>1</v>
+      </c>
+      <c r="CI160" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ160" t="b">
+        <v>1</v>
+      </c>
+      <c r="CK160" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
